--- a/artfynd/A 29756-2023 artfynd.xlsx
+++ b/artfynd/A 29756-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429190</v>
+        <v>123428542</v>
       </c>
       <c r="B2" t="n">
-        <v>91577</v>
+        <v>79718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388406</v>
+        <v>388382</v>
       </c>
       <c r="R2" t="n">
-        <v>6591674</v>
+        <v>6591671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428542</v>
+        <v>123429190</v>
       </c>
       <c r="B3" t="n">
-        <v>79718</v>
+        <v>91577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388382</v>
+        <v>388406</v>
       </c>
       <c r="R3" t="n">
-        <v>6591671</v>
+        <v>6591674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29756-2023 artfynd.xlsx
+++ b/artfynd/A 29756-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428542</v>
+        <v>123429190</v>
       </c>
       <c r="B2" t="n">
-        <v>79718</v>
+        <v>91583</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>388</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388382</v>
+        <v>388406</v>
       </c>
       <c r="R2" t="n">
-        <v>6591671</v>
+        <v>6591674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429190</v>
+        <v>123428542</v>
       </c>
       <c r="B3" t="n">
-        <v>91577</v>
+        <v>79719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388406</v>
+        <v>388382</v>
       </c>
       <c r="R3" t="n">
-        <v>6591674</v>
+        <v>6591671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 29756-2023 artfynd.xlsx
+++ b/artfynd/A 29756-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429190</v>
+        <v>123428542</v>
       </c>
       <c r="B2" t="n">
-        <v>91586</v>
+        <v>79728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388406</v>
+        <v>388382</v>
       </c>
       <c r="R2" t="n">
-        <v>6591674</v>
+        <v>6591671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428542</v>
+        <v>123429190</v>
       </c>
       <c r="B3" t="n">
-        <v>79722</v>
+        <v>91603</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388382</v>
+        <v>388406</v>
       </c>
       <c r="R3" t="n">
-        <v>6591671</v>
+        <v>6591674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29756-2023 artfynd.xlsx
+++ b/artfynd/A 29756-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428542</v>
       </c>
       <c r="B2" t="n">
-        <v>79728</v>
+        <v>79733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>123429190</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>91608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 29756-2023 artfynd.xlsx
+++ b/artfynd/A 29756-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123428542</v>
       </c>
       <c r="B2" t="n">
-        <v>79733</v>
+        <v>79735</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>123429190</v>
       </c>
       <c r="B3" t="n">
-        <v>91608</v>
+        <v>91610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 29756-2023 artfynd.xlsx
+++ b/artfynd/A 29756-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428542</v>
+        <v>123429190</v>
       </c>
       <c r="B2" t="n">
-        <v>79735</v>
+        <v>91610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>388</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388382</v>
+        <v>388406</v>
       </c>
       <c r="R2" t="n">
-        <v>6591671</v>
+        <v>6591674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123429190</v>
+        <v>123428542</v>
       </c>
       <c r="B3" t="n">
-        <v>91610</v>
+        <v>79735</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388406</v>
+        <v>388382</v>
       </c>
       <c r="R3" t="n">
-        <v>6591674</v>
+        <v>6591671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29756-2023 artfynd.xlsx
+++ b/artfynd/A 29756-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123429190</v>
+        <v>123428542</v>
       </c>
       <c r="B2" t="n">
-        <v>91610</v>
+        <v>79735</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388406</v>
+        <v>388382</v>
       </c>
       <c r="R2" t="n">
-        <v>6591674</v>
+        <v>6591671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428542</v>
+        <v>123429190</v>
       </c>
       <c r="B3" t="n">
-        <v>79735</v>
+        <v>91610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388382</v>
+        <v>388406</v>
       </c>
       <c r="R3" t="n">
-        <v>6591671</v>
+        <v>6591674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
